--- a/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration.xlsx
+++ b/jpcore-r4/feature/wg45-familymember-birth-order-label/StructureDefinition-jp-medicationadministration.xlsx
@@ -563,7 +563,7 @@
   <si>
     <t>このインスタンスが外部から参照されるために使われるIDである。処方箋全体としてのIDとしては使用しない。  
 処方箋内で同一の用法をまとめて表記されるRp番号はこのIdentifier elementの別スライスで表現する。それ以外に任意のIDを付与してもよい。  
-このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバからサーバに転送されたとしても固定のものとして存続する。</t>
+このIDは業務手順によって定められた処方オーダに対して、直接的なURL参照が適切でない場合も含めて関連付けるために使われる。この業務手順のIDは実施者によって割り当てられたものであり、リソースが更新されたりサーバーからサーバーに転送されたとしても固定のものとして存続する。</t>
   </si>
   <si>
     <t>これは業務IDであって、リソースに対するIDではない。</t>
@@ -1383,7 +1383,7 @@
   </si>
   <si>
     <t>構造化された注釈情報がないシステムの場合、この要素によって作成者や作成時刻情報なしで単一の注釈を簡単に伝達できる。投与情報に付帯する潜在的な情報や修飾的な情報を伝えるために、この要素に叙述的な記述でそれらを含める必要がある場合がある。   
-*注釈は、計算可能な「変更」情報を伝達するために使用されるべきではない*。 （ユーザの行動を強制することはほとんど不可能であるため、これはSHOULDである）。</t>
+*注釈は、計算可能な「変更」情報を伝達するために使用されるべきではない*。 （ユーザーの行動を強制することはほとんど不可能であるため、これはSHOULDである）。</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -1423,7 +1423,7 @@
     <t>フリーテキストの投与方法の説明　SIG:用法</t>
   </si>
   <si>
-    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコーディングできない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
+    <t>フリーテキストの投与量用法は、投与される投与量や用法が複雑すぎてコード化できない場合に使用できる。コード化された投与量や用法が存在する場合、フリーテキストの投与量や用法は、人間に表示するためにまだ存在している可能性がある。  
 投与量や用法のこの指示は、実際に投与される薬の投与量や用法を反映する必要がある。</t>
   </si>
   <si>
@@ -1542,7 +1542,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法１桁コードを識別するURI。</t>
   </si>
   <si>
-    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコーディング規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
+    <t>コードは臨時で列記したものや、コードのリストからSNOMED CTのように公式に定義されたものまである（HL7 v3 core principle を参照)。FHIR自体ではコード化に関する規約を定めてはいないし、意味を暗示するために利用されない(SHALL NOT)。一般的に UserSelected = trueの場合には一つのコードシステムが使われる。</t>
   </si>
   <si>
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
